--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="8">
   <si>
     <t>update_name</t>
   </si>
@@ -45,6 +45,12 @@
   </si>
   <si>
     <t>牛鬼蛇神</t>
+  </si>
+  <si>
+    <t>崇山乐园</t>
+  </si>
+  <si>
+    <t>2026-02-22</t>
   </si>
 </sst>
 </file>
@@ -1192,8 +1198,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="1"/>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="13.4545454545455" customWidth="1"/>
     <col min="2" max="2" width="11.6363636363636" style="1" customWidth="1"/>
@@ -1231,6 +1237,14 @@
         <v>3</v>
       </c>
     </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="15">
   <si>
     <t>update_name</t>
   </si>
@@ -51,6 +51,27 @@
   </si>
   <si>
     <t>2026-02-22</t>
+  </si>
+  <si>
+    <t>季风吹过橘色的海</t>
+  </si>
+  <si>
+    <t>2026-02-23</t>
+  </si>
+  <si>
+    <t>雪乡连环杀人事件2</t>
+  </si>
+  <si>
+    <t>豆大点事物语</t>
+  </si>
+  <si>
+    <t>盒子先生的秘密商店</t>
+  </si>
+  <si>
+    <t>孤城</t>
+  </si>
+  <si>
+    <t>刀鞘</t>
   </si>
 </sst>
 </file>
@@ -63,13 +84,19 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -536,143 +563,144 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1198,10 +1226,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="1"/>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="13.4545454545455" customWidth="1"/>
+    <col min="1" max="1" width="22.6363636363636" customWidth="1"/>
     <col min="2" max="2" width="11.6363636363636" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1245,6 +1273,54 @@
         <v>7</v>
       </c>
     </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" ht="15" spans="1:2">
+      <c r="A10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" ht="15" spans="1:2">
+      <c r="A11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="21">
   <si>
     <t>update_name</t>
   </si>
@@ -72,6 +72,24 @@
   </si>
   <si>
     <t>刀鞘</t>
+  </si>
+  <si>
+    <t>精神病院4</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>最后的晚餐</t>
+  </si>
+  <si>
+    <t>青白</t>
+  </si>
+  <si>
+    <t>蓝色大丽花</t>
+  </si>
+  <si>
+    <t>此时彼刻之人</t>
   </si>
 </sst>
 </file>
@@ -84,7 +102,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -96,6 +114,12 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -563,137 +587,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -701,6 +725,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1226,7 +1253,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="22.6363636363636" customWidth="1"/>
@@ -1321,6 +1348,46 @@
         <v>9</v>
       </c>
     </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="24">
   <si>
     <t>update_name</t>
   </si>
@@ -90,6 +90,15 @@
   </si>
   <si>
     <t>此时彼刻之人</t>
+  </si>
+  <si>
+    <t>我与我诀别</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>红豆</t>
   </si>
 </sst>
 </file>
@@ -717,7 +726,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -728,6 +737,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1253,7 +1263,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="22.6363636363636" customWidth="1"/>
@@ -1388,6 +1398,22 @@
         <v>16</v>
       </c>
     </row>
+    <row r="17" ht="15" spans="1:2">
+      <c r="A17" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" ht="15" spans="1:2">
+      <c r="A18" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,15 +27,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="26">
   <si>
     <t>update_name</t>
   </si>
   <si>
+    <t>type</t>
+  </si>
+  <si>
     <t>update_date</t>
   </si>
   <si>
     <t>未完待续</t>
+  </si>
+  <si>
+    <t>剧本杀</t>
   </si>
   <si>
     <t>2026-02-21</t>
@@ -726,7 +732,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -737,7 +743,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1263,155 +1268,210 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B18"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="1"/>
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="22.6363636363636" customWidth="1"/>
-    <col min="2" max="2" width="11.6363636363636" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.6363636363636" customWidth="1"/>
+    <col min="3" max="3" width="11.6363636363636" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
+    </row>
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" ht="15" spans="1:2">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" ht="15" spans="1:3">
       <c r="A10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" ht="15" spans="1:2">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" ht="15" spans="1:3">
       <c r="A11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
+        <v>16</v>
+      </c>
+      <c r="B11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
       <c r="A12" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
+        <v>17</v>
+      </c>
+      <c r="B12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
+        <v>19</v>
+      </c>
+      <c r="B13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
       <c r="A14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
+    </row>
+    <row r="15" spans="1:3">
       <c r="A15" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
+        <v>21</v>
+      </c>
+      <c r="B15" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
       <c r="A16" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" ht="15" spans="1:2">
-      <c r="A17" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B17" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="18" ht="15" spans="1:2">
-      <c r="A18" s="4" t="s">
+      <c r="B16" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" ht="15" spans="1:3">
+      <c r="A17" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>22</v>
+      <c r="B17" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" ht="15" spans="1:3">
+      <c r="A18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="32">
   <si>
     <t>update_name</t>
   </si>
@@ -105,6 +105,24 @@
   </si>
   <si>
     <t>红豆</t>
+  </si>
+  <si>
+    <t>长安秘案录</t>
+  </si>
+  <si>
+    <t>小说</t>
+  </si>
+  <si>
+    <t>2026-02-26</t>
+  </si>
+  <si>
+    <t>亡瘾</t>
+  </si>
+  <si>
+    <t>豺狼的日子</t>
+  </si>
+  <si>
+    <t>剧集</t>
   </si>
 </sst>
 </file>
@@ -1268,7 +1286,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="22.6363636363636" customWidth="1"/>
@@ -1474,6 +1492,39 @@
         <v>24</v>
       </c>
     </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="34">
   <si>
     <t>update_name</t>
   </si>
@@ -123,6 +123,12 @@
   </si>
   <si>
     <t>剧集</t>
+  </si>
+  <si>
+    <t>家宴</t>
+  </si>
+  <si>
+    <t>2026-02-27</t>
   </si>
 </sst>
 </file>
@@ -1286,11 +1292,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="22.6363636363636" customWidth="1"/>
-    <col min="2" max="2" width="22.6363636363636" customWidth="1"/>
+    <col min="1" max="2" width="22.6363636363636" customWidth="1"/>
     <col min="3" max="3" width="11.6363636363636" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1525,6 +1530,17 @@
         <v>28</v>
       </c>
     </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/update.xlsx
+++ b/update.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="47">
   <si>
     <t>update_name</t>
   </si>
@@ -129,6 +129,45 @@
   </si>
   <si>
     <t>2026-02-27</t>
+  </si>
+  <si>
+    <t>大宴之上</t>
+  </si>
+  <si>
+    <t>阴明寺</t>
+  </si>
+  <si>
+    <t>死者在幻夜中醒来</t>
+  </si>
+  <si>
+    <t>刑侦现场雪夜追凶</t>
+  </si>
+  <si>
+    <t>生还之日</t>
+  </si>
+  <si>
+    <t>一个死去的朋友</t>
+  </si>
+  <si>
+    <t>生门</t>
+  </si>
+  <si>
+    <t>东京恐怖故事：加藤病院</t>
+  </si>
+  <si>
+    <t>三界之下</t>
+  </si>
+  <si>
+    <t>猫岛2犬山谋杀循环</t>
+  </si>
+  <si>
+    <t>声声慢</t>
+  </si>
+  <si>
+    <t>声声慢2</t>
+  </si>
+  <si>
+    <t>我滴家在东北</t>
   </si>
 </sst>
 </file>
@@ -141,7 +180,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -159,6 +198,12 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -626,137 +671,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -764,6 +809,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1292,7 +1343,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="22.6363636363636" customWidth="1"/>
@@ -1541,6 +1592,149 @@
         <v>33</v>
       </c>
     </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" t="s">
+        <v>4</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" t="s">
+        <v>4</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" t="s">
+        <v>4</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" t="s">
+        <v>4</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" t="s">
+        <v>4</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" t="s">
+        <v>4</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" t="s">
+        <v>4</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" t="s">
+        <v>4</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B35" t="s">
+        <v>4</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
